--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4C7668F-DAD7-4D9D-A28A-72B8773F6941}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E254B9-E862-4E8E-8BAA-DC39C6276513}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B4CD45-8466-4915-8C9A-E4A1CCC3C4EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E5EFD71-6F5C-437F-957D-F9536EEB2C24}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DABD011-C6ED-4159-9ADC-AEE2D7B5F950}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C7BBBD2-1962-463D-A9E9-FBFD5167030A}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E254B9-E862-4E8E-8BAA-DC39C6276513}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47ABAF13-0F20-49E7-BBAA-EA0EB227AE4A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E5EFD71-6F5C-437F-957D-F9536EEB2C24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17DB489F-7050-485F-8589-F83DFC040DE3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C7BBBD2-1962-463D-A9E9-FBFD5167030A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2439DCBD-D994-4569-8DBB-02FE8F3E05C4}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47ABAF13-0F20-49E7-BBAA-EA0EB227AE4A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09BA1837-50C6-473C-AB4D-CC8B3CBD835C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17DB489F-7050-485F-8589-F83DFC040DE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BFFAA58-E81E-4A7F-A9BA-EF8B66BF46F3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2439DCBD-D994-4569-8DBB-02FE8F3E05C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E49304D6-84E8-4417-940C-A0233129D3D2}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3945,22 +3945,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7E254B9-E862-4E8E-8BAA-DC39C6276513}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D788B68D-EE79-4255-BE12-04281A11FDE2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E5EFD71-6F5C-437F-957D-F9536EEB2C24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E685F47D-0B1D-4EA4-82A9-FF499325F7AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C7BBBD2-1962-463D-A9E9-FBFD5167030A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B236A73-8C86-4BDC-BE0A-290AAE98FCFE}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3945,22 +3945,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09BA1837-50C6-473C-AB4D-CC8B3CBD835C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7B5CED3-CFB9-4409-89C1-E3F00439C505}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BFFAA58-E81E-4A7F-A9BA-EF8B66BF46F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AE54FD6-ADF0-40F0-B4C9-08FCA4952BF2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E49304D6-84E8-4417-940C-A0233129D3D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6793F20E-F223-4E55-843E-E647AF39CD81}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7B5CED3-CFB9-4409-89C1-E3F00439C505}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E42ECE63-0F47-4F13-AB8D-48C48D4EDD5E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AE54FD6-ADF0-40F0-B4C9-08FCA4952BF2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8134419-CC93-4294-8855-DF02D1BCD9A8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6793F20E-F223-4E55-843E-E647AF39CD81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C19256D5-BF68-42F5-8B3B-1E5313E12382}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E42ECE63-0F47-4F13-AB8D-48C48D4EDD5E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{777DA59D-4DE4-4051-A50E-840F9E7109FC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8134419-CC93-4294-8855-DF02D1BCD9A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D91A43C7-FD40-4631-9499-943DC41A121D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C19256D5-BF68-42F5-8B3B-1E5313E12382}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A54B3BF6-49BE-4590-85BC-BDCCEB8C2841}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{777DA59D-4DE4-4051-A50E-840F9E7109FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B80E431-2B6C-4865-9B8A-971CD55FB735}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D91A43C7-FD40-4631-9499-943DC41A121D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E81A3A00-E8D8-4BAE-A94A-F329AAACB54F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A54B3BF6-49BE-4590-85BC-BDCCEB8C2841}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAE161D6-1215-447B-AFB1-DAE9516EFEEC}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B80E431-2B6C-4865-9B8A-971CD55FB735}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4CDB0C5-20D9-4546-B733-DF8A1A0E7DC4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E81A3A00-E8D8-4BAE-A94A-F329AAACB54F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{182D9BA1-7092-41A1-A788-9D8C10A9A917}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAE161D6-1215-447B-AFB1-DAE9516EFEEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A60F203-B868-4CC9-857A-ECD069521A91}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4CDB0C5-20D9-4546-B733-DF8A1A0E7DC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A025D947-4D54-491B-89E2-175E158BB450}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{182D9BA1-7092-41A1-A788-9D8C10A9A917}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA037EDA-6670-4ABB-BEC9-02F10A593B98}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A60F203-B868-4CC9-857A-ECD069521A91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C92A1BCD-C66B-4A82-86B5-679FFE8D5318}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A025D947-4D54-491B-89E2-175E158BB450}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52D4E193-A286-495A-8F0E-1F8A77C5831F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA037EDA-6670-4ABB-BEC9-02F10A593B98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B4C85C8-48A3-435A-AC43-7A509ECC6D63}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C92A1BCD-C66B-4A82-86B5-679FFE8D5318}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDABBB09-464A-41F9-BB41-5EE5A5420238}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52D4E193-A286-495A-8F0E-1F8A77C5831F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3450E6E-C4A4-470C-AD3C-CFC5C0BFC6E3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B4C85C8-48A3-435A-AC43-7A509ECC6D63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC681994-D3FB-406C-AB13-06642831523A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDABBB09-464A-41F9-BB41-5EE5A5420238}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7AC93A6-DF17-4FCB-819A-54ED279EF3A7}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3450E6E-C4A4-470C-AD3C-CFC5C0BFC6E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60A95E9-D5C3-4A8E-8FAD-9D371A6652BB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC681994-D3FB-406C-AB13-06642831523A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CD1E10D-B023-4F2B-BC7C-5B6315FF56FF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7AC93A6-DF17-4FCB-819A-54ED279EF3A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD058E8B-866F-42DA-B930-D4CDA9365B09}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60A95E9-D5C3-4A8E-8FAD-9D371A6652BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1702A7EF-8019-4BC9-B4E9-88F6B896C175}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CD1E10D-B023-4F2B-BC7C-5B6315FF56FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B4A8D5D-2AFB-4A16-ADEB-32B04A92269B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD058E8B-866F-42DA-B930-D4CDA9365B09}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A2BBE9-555E-4DB9-A405-D818D5E4D5C2}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1702A7EF-8019-4BC9-B4E9-88F6B896C175}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABD9C44B-399C-435A-BEB5-40C207EB380D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B4A8D5D-2AFB-4A16-ADEB-32B04A92269B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AF2C2DA-E14F-4FC5-A528-EB62EFBAF77E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A2BBE9-555E-4DB9-A405-D818D5E4D5C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C484EDED-E3F2-4874-AC21-51D5DBC65BBF}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABD9C44B-399C-435A-BEB5-40C207EB380D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F84A3D8-F414-40F7-BA8D-72A98A3ED291}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AF2C2DA-E14F-4FC5-A528-EB62EFBAF77E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF859A65-CF27-43C0-8EBA-BD196E992B65}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C484EDED-E3F2-4874-AC21-51D5DBC65BBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52BE5CF8-C083-4C2E-9461-4FCEDD5E4319}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F84A3D8-F414-40F7-BA8D-72A98A3ED291}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{534E3D4A-A79D-4083-839D-8658C2BFDAF6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF859A65-CF27-43C0-8EBA-BD196E992B65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5B830DE-DD7F-46D0-B67E-13474A74CE0C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52BE5CF8-C083-4C2E-9461-4FCEDD5E4319}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC310CF4-E9F1-4FF8-A74C-C03D808B2C76}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{534E3D4A-A79D-4083-839D-8658C2BFDAF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E9AFCA-E347-4377-97F5-1CDC68A16109}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5B830DE-DD7F-46D0-B67E-13474A74CE0C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F6B1FAE-1524-42DB-916D-E937CCB95F1B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC310CF4-E9F1-4FF8-A74C-C03D808B2C76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30255B26-5CF8-4605-BF21-329BFDB5B57A}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E9AFCA-E347-4377-97F5-1CDC68A16109}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C85E34F5-3F5B-41CC-B249-FA6D088BA547}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F6B1FAE-1524-42DB-916D-E937CCB95F1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB057CD6-9C1E-49C9-815F-51A805B22577}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30255B26-5CF8-4605-BF21-329BFDB5B57A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8400EFBE-1A7E-4EB6-A8CD-36767D591970}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C85E34F5-3F5B-41CC-B249-FA6D088BA547}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29987FF3-1FD0-452A-B7B1-F70716E810F1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB057CD6-9C1E-49C9-815F-51A805B22577}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{377B045E-9DF2-4D2F-AB4E-96A55AC427DA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8400EFBE-1A7E-4EB6-A8CD-36767D591970}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9008AB80-FEBE-4DA0-AB26-D72F2431C2C0}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29987FF3-1FD0-452A-B7B1-F70716E810F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75A954B8-410D-4AAB-84A6-98914823C2E6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{377B045E-9DF2-4D2F-AB4E-96A55AC427DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2F9708C-1CDA-492C-A109-21B282411A92}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9008AB80-FEBE-4DA0-AB26-D72F2431C2C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEC6DBF4-CE9C-4170-97A3-9AD966D71216}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75A954B8-410D-4AAB-84A6-98914823C2E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F24E9-4F18-4147-A9CF-373B755A5C05}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2F9708C-1CDA-492C-A109-21B282411A92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA25711-1CC6-47CA-B807-B1161868F1C0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEC6DBF4-CE9C-4170-97A3-9AD966D71216}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B023C6E3-E735-42D3-AAFB-1301F8B2210E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{416F24E9-4F18-4147-A9CF-373B755A5C05}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09D23450-C461-4EC9-A37B-5CE6113ACF83}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEA25711-1CC6-47CA-B807-B1161868F1C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03065A78-0C08-429E-83DF-08D58607EE91}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B023C6E3-E735-42D3-AAFB-1301F8B2210E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{132C8EFE-0D90-42D2-804A-B14A30C626D3}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09D23450-C461-4EC9-A37B-5CE6113ACF83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C014377-6C98-4FAA-9941-DB008ECACDEE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03065A78-0C08-429E-83DF-08D58607EE91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A4D20D-9825-4288-9053-8DC8B2A7C207}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{132C8EFE-0D90-42D2-804A-B14A30C626D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35CB4F1B-AC9F-4F92-9930-84548F76A068}"/>
 </file>